--- a/public/plantillas/11_PROG_UTILIZACION_HERRAMIENTAS.xlsx
+++ b/public/plantillas/11_PROG_UTILIZACION_HERRAMIENTAS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ventura/Desktop/Programacion/recal-hse/public/plantillas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1007980A-FE91-D640-9152-D28F45259D92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DD15664-7777-F343-A916-315157F2E974}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3620" yWindow="0" windowWidth="29980" windowHeight="21000" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="54">
   <si>
     <t>PROGRAMA DE UTILIZACIÓN DE MAQUINARIA Y EQUIPO</t>
   </si>
@@ -182,10 +182,6 @@
     <t>CONTRATISTA: RECAL ESTRUCTURAS</t>
   </si>
   <si>
-    <t xml:space="preserve">
-OBSERVACIONES:</t>
-  </si>
-  <si>
     <t xml:space="preserve">FECHA: </t>
   </si>
   <si>
@@ -207,13 +203,7 @@
     <t>ELABORÓ</t>
   </si>
   <si>
-    <t>AUTORIZÓ</t>
-  </si>
-  <si>
-    <t>ANTONIO SATURNO FRANCISCO RAMON</t>
-  </si>
-  <si>
-    <t>OSVALDO JIMENEZ MORALES</t>
+    <t>OBSERVACIONES:</t>
   </si>
 </sst>
 </file>
@@ -377,7 +367,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -505,11 +495,31 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -572,9 +582,37 @@
     <xf numFmtId="0" fontId="13" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -602,17 +640,35 @@
     <xf numFmtId="0" fontId="16" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -623,35 +679,8 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1370,7 +1399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U984"/>
+  <dimension ref="A1:U985"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.5" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="9.83203125" customWidth="1"/>
@@ -1385,42 +1414,42 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="60" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="23" t="s">
-        <v>50</v>
-      </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
-      <c r="H1" s="23"/>
+      <c r="A1" s="33" t="s">
+        <v>49</v>
+      </c>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
+      <c r="H1" s="33"/>
     </row>
     <row r="2" spans="1:21" ht="27" x14ac:dyDescent="0.15">
-      <c r="A2" s="29" t="s">
-        <v>52</v>
-      </c>
-      <c r="B2" s="30"/>
-      <c r="C2" s="30"/>
-      <c r="D2" s="31"/>
-      <c r="E2" s="24" t="s">
-        <v>47</v>
-      </c>
-      <c r="F2" s="25"/>
-      <c r="G2" s="25"/>
-      <c r="H2" s="25"/>
+      <c r="A2" s="39" t="s">
+        <v>51</v>
+      </c>
+      <c r="B2" s="40"/>
+      <c r="C2" s="40"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="34" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2" s="35"/>
+      <c r="G2" s="35"/>
+      <c r="H2" s="35"/>
     </row>
     <row r="3" spans="1:21" ht="49" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="24" t="s">
+      <c r="A3" s="34" t="s">
         <v>45</v>
       </c>
-      <c r="B3" s="25"/>
-      <c r="C3" s="25"/>
-      <c r="D3" s="28"/>
-      <c r="E3" s="26"/>
-      <c r="F3" s="27"/>
-      <c r="G3" s="27"/>
-      <c r="H3" s="27"/>
+      <c r="B3" s="35"/>
+      <c r="C3" s="35"/>
+      <c r="D3" s="38"/>
+      <c r="E3" s="36"/>
+      <c r="F3" s="37"/>
+      <c r="G3" s="37"/>
+      <c r="H3" s="37"/>
     </row>
     <row r="4" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="13" t="s">
@@ -1436,13 +1465,13 @@
         <v>7</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F4" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="G4" s="15" t="s">
         <v>48</v>
-      </c>
-      <c r="G4" s="15" t="s">
-        <v>49</v>
       </c>
       <c r="H4" s="18" t="s">
         <v>11</v>
@@ -1458,62 +1487,67 @@
       <c r="G5" s="17"/>
       <c r="H5" s="16"/>
     </row>
-    <row r="6" spans="1:21" ht="69" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="22" t="s">
-        <v>46</v>
-      </c>
-      <c r="B6" s="22"/>
-      <c r="C6" s="22"/>
-      <c r="D6" s="22"/>
-      <c r="E6" s="22"/>
-      <c r="F6" s="22"/>
-      <c r="G6" s="22"/>
-      <c r="H6" s="22"/>
+    <row r="6" spans="1:21" ht="157" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A6" s="19"/>
+      <c r="B6" s="20"/>
+      <c r="C6" s="19"/>
+      <c r="D6" s="21"/>
+      <c r="E6" s="19"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="17"/>
+      <c r="H6" s="16"/>
     </row>
-    <row r="7" spans="1:21" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="32" t="s">
+    <row r="7" spans="1:21" ht="69" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A7" s="55" t="s">
         <v>53</v>
       </c>
-      <c r="B7" s="33"/>
-      <c r="C7" s="33"/>
-      <c r="D7" s="33"/>
-      <c r="E7" s="32" t="s">
-        <v>54</v>
-      </c>
-      <c r="F7" s="33"/>
-      <c r="G7" s="33"/>
-      <c r="H7" s="33"/>
-      <c r="J7" s="12"/>
-      <c r="K7" s="12"/>
-      <c r="L7" s="12"/>
-      <c r="M7" s="12"/>
-      <c r="N7" s="12"/>
-      <c r="O7" s="12"/>
-      <c r="P7" s="12"/>
-      <c r="Q7" s="12"/>
-      <c r="R7" s="12"/>
-      <c r="S7" s="12"/>
-      <c r="T7" s="12"/>
-      <c r="U7" s="12"/>
+      <c r="B7" s="23"/>
+      <c r="C7" s="23"/>
+      <c r="D7" s="23"/>
+      <c r="E7" s="23"/>
+      <c r="F7" s="23"/>
+      <c r="G7" s="23"/>
+      <c r="H7" s="24"/>
     </row>
-    <row r="8" spans="1:21" ht="81" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="34" t="s">
-        <v>56</v>
-      </c>
-      <c r="B8" s="35"/>
-      <c r="C8" s="35"/>
-      <c r="D8" s="35"/>
-      <c r="E8" s="34" t="s">
-        <v>55</v>
-      </c>
-      <c r="F8" s="35"/>
-      <c r="G8" s="35"/>
-      <c r="H8" s="35"/>
+    <row r="8" spans="1:21" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A8" s="25"/>
+      <c r="B8" s="26"/>
+      <c r="C8" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="D8" s="26"/>
+      <c r="E8" s="25"/>
+      <c r="F8" s="28" t="s">
+        <v>41</v>
+      </c>
+      <c r="G8" s="26"/>
+      <c r="H8" s="26"/>
+      <c r="J8" s="12"/>
+      <c r="K8" s="12"/>
+      <c r="L8" s="12"/>
+      <c r="M8" s="12"/>
+      <c r="N8" s="12"/>
+      <c r="O8" s="12"/>
+      <c r="P8" s="12"/>
+      <c r="Q8" s="12"/>
+      <c r="R8" s="12"/>
+      <c r="S8" s="12"/>
+      <c r="T8" s="12"/>
+      <c r="U8" s="12"/>
     </row>
-    <row r="9" spans="1:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="10" spans="1:21" ht="52.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="11" spans="1:21" ht="8.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="12" spans="1:21" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="9" spans="1:21" ht="81" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="29"/>
+      <c r="B9" s="30"/>
+      <c r="C9" s="22"/>
+      <c r="D9" s="31"/>
+      <c r="E9" s="29"/>
+      <c r="F9" s="32"/>
+      <c r="G9" s="30"/>
+      <c r="H9" s="30"/>
+    </row>
+    <row r="10" spans="1:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="11" spans="1:21" ht="52.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="12" spans="1:21" ht="8.25" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="13" spans="1:21" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="14" spans="1:21" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="15" spans="1:21" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
@@ -2486,13 +2520,9 @@
     <row r="982" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="983" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="984" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="985" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
   </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A7:D7"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="E8:H8"/>
-    <mergeCell ref="E7:H7"/>
-    <mergeCell ref="A6:H6"/>
+  <mergeCells count="5">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="E2:H2"/>
     <mergeCell ref="E3:H3"/>
@@ -2530,59 +2560,59 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="60" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
-      <c r="H1" s="23"/>
-      <c r="I1" s="23"/>
-      <c r="J1" s="23"/>
-      <c r="K1" s="23"/>
-      <c r="L1" s="23"/>
-      <c r="M1" s="23"/>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
+      <c r="H1" s="33"/>
+      <c r="I1" s="33"/>
+      <c r="J1" s="33"/>
+      <c r="K1" s="33"/>
+      <c r="L1" s="33"/>
+      <c r="M1" s="33"/>
     </row>
     <row r="2" spans="1:26" ht="20" x14ac:dyDescent="0.15">
-      <c r="A2" s="36" t="s">
+      <c r="A2" s="52" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="36"/>
-      <c r="C2" s="36"/>
-      <c r="D2" s="36"/>
-      <c r="E2" s="36"/>
-      <c r="F2" s="37" t="s">
+      <c r="B2" s="52"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="53" t="s">
         <v>44</v>
       </c>
-      <c r="G2" s="37"/>
-      <c r="H2" s="37"/>
-      <c r="I2" s="37"/>
-      <c r="J2" s="37"/>
-      <c r="K2" s="37"/>
-      <c r="L2" s="37"/>
-      <c r="M2" s="37"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
+      <c r="I2" s="53"/>
+      <c r="J2" s="53"/>
+      <c r="K2" s="53"/>
+      <c r="L2" s="53"/>
+      <c r="M2" s="53"/>
     </row>
     <row r="3" spans="1:26" ht="26.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="36" t="s">
+      <c r="A3" s="52" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="36"/>
-      <c r="C3" s="36"/>
-      <c r="D3" s="36"/>
-      <c r="E3" s="36"/>
-      <c r="F3" s="38" t="s">
+      <c r="B3" s="52"/>
+      <c r="C3" s="52"/>
+      <c r="D3" s="52"/>
+      <c r="E3" s="52"/>
+      <c r="F3" s="54" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="38"/>
-      <c r="H3" s="38"/>
-      <c r="I3" s="38"/>
-      <c r="J3" s="38"/>
-      <c r="K3" s="38"/>
-      <c r="L3" s="38"/>
-      <c r="M3" s="38"/>
+      <c r="G3" s="54"/>
+      <c r="H3" s="54"/>
+      <c r="I3" s="54"/>
+      <c r="J3" s="54"/>
+      <c r="K3" s="54"/>
+      <c r="L3" s="54"/>
+      <c r="M3" s="54"/>
     </row>
     <row r="4" spans="1:26" ht="36.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="2" t="s">
@@ -2600,20 +2630,20 @@
       <c r="E4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="39" t="s">
+      <c r="F4" s="50" t="s">
         <v>9</v>
       </c>
-      <c r="G4" s="39"/>
-      <c r="H4" s="39" t="s">
+      <c r="G4" s="50"/>
+      <c r="H4" s="50" t="s">
         <v>10</v>
       </c>
-      <c r="I4" s="39"/>
-      <c r="J4" s="40" t="s">
+      <c r="I4" s="50"/>
+      <c r="J4" s="51" t="s">
         <v>11</v>
       </c>
-      <c r="K4" s="40"/>
-      <c r="L4" s="40"/>
-      <c r="M4" s="40"/>
+      <c r="K4" s="51"/>
+      <c r="L4" s="51"/>
+      <c r="M4" s="51"/>
     </row>
     <row r="5" spans="1:26" ht="207.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="4">
@@ -2631,18 +2661,18 @@
       <c r="E5" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="F5" s="41" t="s">
+      <c r="F5" s="48" t="s">
         <v>16</v>
       </c>
-      <c r="G5" s="41"/>
-      <c r="H5" s="42" t="s">
+      <c r="G5" s="48"/>
+      <c r="H5" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="I5" s="42"/>
-      <c r="J5" s="43"/>
-      <c r="K5" s="43"/>
-      <c r="L5" s="43"/>
-      <c r="M5" s="43"/>
+      <c r="I5" s="43"/>
+      <c r="J5" s="49"/>
+      <c r="K5" s="49"/>
+      <c r="L5" s="49"/>
+      <c r="M5" s="49"/>
     </row>
     <row r="6" spans="1:26" ht="207.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="4">
@@ -2660,18 +2690,18 @@
       <c r="E6" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="F6" s="41" t="s">
+      <c r="F6" s="48" t="s">
         <v>16</v>
       </c>
-      <c r="G6" s="41"/>
-      <c r="H6" s="42" t="s">
+      <c r="G6" s="48"/>
+      <c r="H6" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="I6" s="42"/>
-      <c r="J6" s="43"/>
-      <c r="K6" s="43"/>
-      <c r="L6" s="43"/>
-      <c r="M6" s="43"/>
+      <c r="I6" s="43"/>
+      <c r="J6" s="49"/>
+      <c r="K6" s="49"/>
+      <c r="L6" s="49"/>
+      <c r="M6" s="49"/>
     </row>
     <row r="7" spans="1:26" ht="207.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="4">
@@ -2689,18 +2719,18 @@
       <c r="E7" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="F7" s="41" t="s">
+      <c r="F7" s="48" t="s">
         <v>22</v>
       </c>
-      <c r="G7" s="41"/>
-      <c r="H7" s="42" t="s">
+      <c r="G7" s="48"/>
+      <c r="H7" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="I7" s="42"/>
-      <c r="J7" s="43"/>
-      <c r="K7" s="43"/>
-      <c r="L7" s="43"/>
-      <c r="M7" s="43"/>
+      <c r="I7" s="43"/>
+      <c r="J7" s="49"/>
+      <c r="K7" s="49"/>
+      <c r="L7" s="49"/>
+      <c r="M7" s="49"/>
     </row>
     <row r="8" spans="1:26" ht="208.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="4">
@@ -2718,18 +2748,18 @@
       <c r="E8" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="F8" s="42" t="s">
+      <c r="F8" s="43" t="s">
         <v>26</v>
       </c>
-      <c r="G8" s="42"/>
-      <c r="H8" s="42" t="s">
+      <c r="G8" s="43"/>
+      <c r="H8" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="I8" s="42"/>
-      <c r="J8" s="43"/>
-      <c r="K8" s="43"/>
-      <c r="L8" s="43"/>
-      <c r="M8" s="43"/>
+      <c r="I8" s="43"/>
+      <c r="J8" s="49"/>
+      <c r="K8" s="49"/>
+      <c r="L8" s="49"/>
+      <c r="M8" s="49"/>
     </row>
     <row r="9" spans="1:26" ht="208.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
@@ -2747,14 +2777,14 @@
       <c r="E9" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="F9" s="41" t="s">
+      <c r="F9" s="48" t="s">
         <v>30</v>
       </c>
-      <c r="G9" s="41"/>
-      <c r="H9" s="42" t="s">
+      <c r="G9" s="48"/>
+      <c r="H9" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="I9" s="42"/>
+      <c r="I9" s="43"/>
       <c r="J9" s="44"/>
       <c r="K9" s="44"/>
       <c r="L9" s="44"/>
@@ -2776,14 +2806,14 @@
       <c r="E10" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="41" t="s">
+      <c r="F10" s="48" t="s">
         <v>30</v>
       </c>
-      <c r="G10" s="41"/>
-      <c r="H10" s="42" t="s">
+      <c r="G10" s="48"/>
+      <c r="H10" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="I10" s="42"/>
+      <c r="I10" s="43"/>
       <c r="J10" s="44"/>
       <c r="K10" s="44"/>
       <c r="L10" s="44"/>
@@ -2805,14 +2835,14 @@
       <c r="E11" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="F11" s="42" t="s">
+      <c r="F11" s="43" t="s">
         <v>36</v>
       </c>
-      <c r="G11" s="42"/>
-      <c r="H11" s="42" t="s">
+      <c r="G11" s="43"/>
+      <c r="H11" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="I11" s="42"/>
+      <c r="I11" s="43"/>
       <c r="J11" s="44"/>
       <c r="K11" s="44"/>
       <c r="L11" s="44"/>
@@ -2834,54 +2864,54 @@
       <c r="E12" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="F12" s="42" t="s">
+      <c r="F12" s="43" t="s">
         <v>36</v>
       </c>
-      <c r="G12" s="42"/>
-      <c r="H12" s="42" t="s">
+      <c r="G12" s="43"/>
+      <c r="H12" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="I12" s="42"/>
+      <c r="I12" s="43"/>
       <c r="J12" s="44"/>
       <c r="K12" s="44"/>
       <c r="L12" s="44"/>
       <c r="M12" s="44"/>
     </row>
     <row r="13" spans="1:26" ht="69" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="46" t="s">
+      <c r="A13" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="B13" s="46"/>
-      <c r="C13" s="46"/>
-      <c r="D13" s="46"/>
-      <c r="E13" s="46"/>
-      <c r="F13" s="46"/>
-      <c r="G13" s="46"/>
-      <c r="H13" s="46"/>
-      <c r="I13" s="46"/>
-      <c r="J13" s="46"/>
-      <c r="K13" s="46"/>
-      <c r="L13" s="46"/>
-      <c r="M13" s="46"/>
+      <c r="B13" s="45"/>
+      <c r="C13" s="45"/>
+      <c r="D13" s="45"/>
+      <c r="E13" s="45"/>
+      <c r="F13" s="45"/>
+      <c r="G13" s="45"/>
+      <c r="H13" s="45"/>
+      <c r="I13" s="45"/>
+      <c r="J13" s="45"/>
+      <c r="K13" s="45"/>
+      <c r="L13" s="45"/>
+      <c r="M13" s="45"/>
     </row>
     <row r="14" spans="1:26" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="47" t="s">
+      <c r="A14" s="46" t="s">
         <v>40</v>
       </c>
-      <c r="B14" s="47"/>
-      <c r="C14" s="47"/>
-      <c r="D14" s="47"/>
-      <c r="E14" s="47"/>
-      <c r="F14" s="48" t="s">
+      <c r="B14" s="46"/>
+      <c r="C14" s="46"/>
+      <c r="D14" s="46"/>
+      <c r="E14" s="46"/>
+      <c r="F14" s="47" t="s">
         <v>41</v>
       </c>
-      <c r="G14" s="48"/>
-      <c r="H14" s="48"/>
-      <c r="I14" s="48"/>
-      <c r="J14" s="48"/>
-      <c r="K14" s="48"/>
-      <c r="L14" s="48"/>
-      <c r="M14" s="48"/>
+      <c r="G14" s="47"/>
+      <c r="H14" s="47"/>
+      <c r="I14" s="47"/>
+      <c r="J14" s="47"/>
+      <c r="K14" s="47"/>
+      <c r="L14" s="47"/>
+      <c r="M14" s="47"/>
       <c r="N14" s="12"/>
       <c r="O14" s="12"/>
       <c r="P14" s="12"/>
@@ -2897,23 +2927,23 @@
       <c r="Z14" s="12"/>
     </row>
     <row r="15" spans="1:26" ht="81" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A15" s="45" t="s">
+      <c r="A15" s="42" t="s">
         <v>42</v>
       </c>
-      <c r="B15" s="45"/>
-      <c r="C15" s="45"/>
-      <c r="D15" s="45"/>
-      <c r="E15" s="45"/>
-      <c r="F15" s="45" t="s">
+      <c r="B15" s="42"/>
+      <c r="C15" s="42"/>
+      <c r="D15" s="42"/>
+      <c r="E15" s="42"/>
+      <c r="F15" s="42" t="s">
         <v>43</v>
       </c>
-      <c r="G15" s="45"/>
-      <c r="H15" s="45"/>
-      <c r="I15" s="45"/>
-      <c r="J15" s="45"/>
-      <c r="K15" s="45"/>
-      <c r="L15" s="45"/>
-      <c r="M15" s="45"/>
+      <c r="G15" s="42"/>
+      <c r="H15" s="42"/>
+      <c r="I15" s="42"/>
+      <c r="J15" s="42"/>
+      <c r="K15" s="42"/>
+      <c r="L15" s="42"/>
+      <c r="M15" s="42"/>
     </row>
     <row r="16" spans="1:26" ht="30.75" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="17" ht="52.5" customHeight="1" x14ac:dyDescent="0.15"/>
@@ -3893,6 +3923,35 @@
     <row r="991" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
   </sheetData>
   <mergeCells count="37">
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="F2:M2"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="F3:M3"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="J4:M4"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="J5:M5"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="J6:M6"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="J7:M7"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="J8:M8"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="H9:I9"/>
+    <mergeCell ref="J9:M9"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="H10:I10"/>
+    <mergeCell ref="J10:M10"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="H11:I11"/>
+    <mergeCell ref="J11:M11"/>
     <mergeCell ref="A15:E15"/>
     <mergeCell ref="F15:M15"/>
     <mergeCell ref="F12:G12"/>
@@ -3901,35 +3960,6 @@
     <mergeCell ref="A13:M13"/>
     <mergeCell ref="A14:E14"/>
     <mergeCell ref="F14:M14"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="H10:I10"/>
-    <mergeCell ref="J10:M10"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="H11:I11"/>
-    <mergeCell ref="J11:M11"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="J8:M8"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="H9:I9"/>
-    <mergeCell ref="J9:M9"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="J6:M6"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="H7:I7"/>
-    <mergeCell ref="J7:M7"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="J4:M4"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="J5:M5"/>
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="F2:M2"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="F3:M3"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.23611111111111099" right="0.23611111111111099" top="0.74791666666666701" bottom="0.74791666666666701" header="0.511811023622047" footer="0.511811023622047"/>

--- a/public/plantillas/11_PROG_UTILIZACION_HERRAMIENTAS.xlsx
+++ b/public/plantillas/11_PROG_UTILIZACION_HERRAMIENTAS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ventura/Desktop/Programacion/recal-hse/public/plantillas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36015689-7231-5A45-AA76-5184159F4C3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9292E80-AF9E-A54F-B179-10B0F90A7452}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3620" yWindow="0" windowWidth="29980" windowHeight="21000" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -733,7 +733,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U985"/>
+  <dimension ref="A1:U984"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.5" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="9.83203125" customWidth="1"/>
@@ -821,67 +821,58 @@
       <c r="G5" s="7"/>
       <c r="H5" s="6"/>
     </row>
-    <row r="6" spans="1:21" ht="157" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="9"/>
-      <c r="B6" s="10"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="11"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
-      <c r="H6" s="6"/>
-    </row>
-    <row r="7" spans="1:21" ht="69" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="23" t="s">
+    <row r="6" spans="1:21" ht="69" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A6" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="13"/>
-      <c r="C7" s="13"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
-      <c r="F7" s="13"/>
-      <c r="G7" s="13"/>
-      <c r="H7" s="14"/>
+      <c r="B6" s="13"/>
+      <c r="C6" s="13"/>
+      <c r="D6" s="13"/>
+      <c r="E6" s="13"/>
+      <c r="F6" s="13"/>
+      <c r="G6" s="13"/>
+      <c r="H6" s="14"/>
     </row>
-    <row r="8" spans="1:21" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="15"/>
-      <c r="B8" s="16"/>
-      <c r="C8" s="17" t="s">
+    <row r="7" spans="1:21" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A7" s="15"/>
+      <c r="B7" s="16"/>
+      <c r="C7" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="D8" s="16"/>
-      <c r="E8" s="15"/>
-      <c r="F8" s="18" t="s">
+      <c r="D7" s="16"/>
+      <c r="E7" s="15"/>
+      <c r="F7" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="G8" s="16"/>
-      <c r="H8" s="16"/>
-      <c r="J8" s="2"/>
-      <c r="K8" s="2"/>
-      <c r="L8" s="2"/>
-      <c r="M8" s="2"/>
-      <c r="N8" s="2"/>
-      <c r="O8" s="2"/>
-      <c r="P8" s="2"/>
-      <c r="Q8" s="2"/>
-      <c r="R8" s="2"/>
-      <c r="S8" s="2"/>
-      <c r="T8" s="2"/>
-      <c r="U8" s="2"/>
+      <c r="G7" s="16"/>
+      <c r="H7" s="16"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="2"/>
+      <c r="L7" s="2"/>
+      <c r="M7" s="2"/>
+      <c r="N7" s="2"/>
+      <c r="O7" s="2"/>
+      <c r="P7" s="2"/>
+      <c r="Q7" s="2"/>
+      <c r="R7" s="2"/>
+      <c r="S7" s="2"/>
+      <c r="T7" s="2"/>
+      <c r="U7" s="2"/>
     </row>
-    <row r="9" spans="1:21" ht="81" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="19"/>
-      <c r="B9" s="20"/>
-      <c r="C9" s="12"/>
-      <c r="D9" s="21"/>
-      <c r="E9" s="19"/>
-      <c r="F9" s="22"/>
-      <c r="G9" s="20"/>
-      <c r="H9" s="20"/>
+    <row r="8" spans="1:21" ht="81" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="19"/>
+      <c r="B8" s="20"/>
+      <c r="C8" s="12"/>
+      <c r="D8" s="21"/>
+      <c r="E8" s="19"/>
+      <c r="F8" s="22"/>
+      <c r="G8" s="20"/>
+      <c r="H8" s="20"/>
     </row>
-    <row r="10" spans="1:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="11" spans="1:21" ht="52.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="12" spans="1:21" ht="8.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="9" spans="1:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="10" spans="1:21" ht="52.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="11" spans="1:21" ht="8.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="12" spans="1:21" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="13" spans="1:21" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="14" spans="1:21" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="15" spans="1:21" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
@@ -1854,7 +1845,6 @@
     <row r="982" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="983" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="984" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="985" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A1:H1"/>
